--- a/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C8" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D8" s="229" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="C10" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D10" s="229" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="C11" s="205" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D11" s="205" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="C12" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D12" s="229" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C13" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D13" s="229" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C14" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D14" s="229" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="C15" s="205" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D15" s="205" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="C17" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D17" s="229" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C20" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D20" s="229" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="C21" s="205" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D21" s="205" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="C22" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D22" s="229" t="inlineStr">
@@ -3975,7 +3975,7 @@
       <c r="H22" s="238" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco → bấm "Hoạt động"
-2. Tap vào card đơn "Chờ ghép"</t>
+2. Bấm vào card đơn "Chờ ghép"</t>
         </is>
       </c>
       <c r="I22" s="238" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C23" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D23" s="229" t="inlineStr">
@@ -4080,7 +4080,7 @@
       <c r="H23" s="238" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco → bấm "Hoạt động"
-2. Tap vào card đơn "Đã ghép"</t>
+2. Bấm vào card đơn "Đã ghép"</t>
         </is>
       </c>
       <c r="I23" s="238" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C24" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D24" s="229" t="inlineStr">
@@ -4185,7 +4185,7 @@
       <c r="H24" s="238" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco → bấm "Hoạt động"
-2. Tap vào card đơn "Đang giao"</t>
+2. Bấm vào card đơn "Đang giao"</t>
         </is>
       </c>
       <c r="I24" s="238" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="C25" s="205" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D25" s="205" t="inlineStr">
@@ -4290,7 +4290,7 @@
       <c r="H25" s="237" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco → bấm "Hoạt động" → tab "Đã hoàn thành"
-2. Tap vào card đơn "Hoàn thành"</t>
+2. Bấm vào card đơn "Hoàn thành"</t>
         </is>
       </c>
       <c r="I25" s="237" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C26" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D26" s="229" t="inlineStr">
@@ -4395,7 +4395,7 @@
       <c r="H26" s="238" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco → bấm "Hoạt động" → tab "Đã hoàn thành"
-2. Tap vào card có badge "Hết hạn"</t>
+2. Bấm vào card có badge "Hết hạn"</t>
         </is>
       </c>
       <c r="I26" s="238" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="C27" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Chờ BA bổ sung</t>
         </is>
       </c>
       <c r="D27" s="229" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C28" s="229" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Chờ BA bổ sung</t>
         </is>
       </c>
       <c r="D28" s="229" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="C29" s="205" t="inlineStr">
         <is>
-          <t>Quan sát thực tế app</t>
+          <t>Chờ BA bổ sung</t>
         </is>
       </c>
       <c r="D29" s="205" t="inlineStr">

--- a/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
@@ -456,7 +456,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill/>
     </fill>
@@ -665,6 +665,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -902,7 +907,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1626,6 +1631,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3542,7 +3548,7 @@
       </c>
       <c r="F18" s="237" t="inlineStr">
         <is>
-          <t>Check tin tự động chuyển "Hết hạn" khi quá thời gian đăng, hiển thị đúng tại Hoạt động</t>
+          <t>Check tin tự động chuyển "Hết hạn" khi quá "Đến ngày", hiển thị đúng tại Hoạt động</t>
         </is>
       </c>
       <c r="G18" s="237" t="inlineStr">
@@ -3617,7 +3623,7 @@
       </c>
       <c r="AP18" s="225" t="inlineStr">
         <is>
-          <t>Technique: BVA-at-expiry (baseline) | Xem BVA-before-expiry TC kế tiếp cho boundary trước hạn</t>
+          <t>Technique: BVA-at-expiry (baseline) | Xem BVA-before-expiry TC kế tiếp cho boundary trước hạn | Nguồn: merge CA v1.1 `C-ORDER-2` — v1.0 từng chốt ngưỡng EXPIRED = "Từ ngày"; BRD v3.2 ghi rõ 2 lần là "Đến ngày" và user xác nhận lại "Den ngay dung" (đảo ngược resolution cũ). Nhãn TC làm rõ để không đọc nhầm thành "Từ ngày"</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3654,7 @@
       </c>
       <c r="F19" s="238" t="inlineStr">
         <is>
-          <t>Check tin CHƯA tự động chuyển "Hết hạn" khi còn trong hạn (boundary ngay trước hạn)</t>
+          <t>Check tin CHƯA tự động chuyển "Hết hạn" khi CHƯA tới "Đến ngày" (boundary ngay trước hạn)</t>
         </is>
       </c>
       <c r="G19" s="238" t="inlineStr">
@@ -3723,7 +3729,7 @@
       </c>
       <c r="AP19" s="234" t="inlineStr">
         <is>
-          <t>Technique: BVA-before-expiry | Cần bổ sung test data trong catalog (catalog chưa có mốc hạn tin cụ thể để dựng boundary chính xác)</t>
+          <t>Technique: BVA-before-expiry | Cần bổ sung test data trong catalog (catalog chưa có mốc hạn tin cụ thể để dựng boundary chính xác) | Nguồn: merge CA v1.1 `C-ORDER-2` — v1.0 từng chốt ngưỡng EXPIRED = "Từ ngày"; BRD v3.2 ghi rõ 2 lần là "Đến ngày" và user xác nhận lại "Den ngay dung" (đảo ngược resolution cũ). Nhãn TC làm rõ để không đọc nhầm thành "Từ ngày"</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3970,7 @@
       </c>
       <c r="F22" s="238" t="inlineStr">
         <is>
-          <t>Check tap vào card trạng thái "Chờ ghép" mở đúng màn Chi tiết tin</t>
+          <t>Check bấm vào card trạng thái "Chờ ghép" mở đúng màn Chi tiết tin</t>
         </is>
       </c>
       <c r="G22" s="238" t="inlineStr">
@@ -4069,7 +4075,7 @@
       </c>
       <c r="F23" s="238" t="inlineStr">
         <is>
-          <t>Check tap vào card trạng thái "Đã ghép" mở đúng màn Chi tiết tin</t>
+          <t>Check bấm vào card trạng thái "Đã ghép" mở đúng màn Chi tiết tin</t>
         </is>
       </c>
       <c r="G23" s="238" t="inlineStr">
@@ -4174,7 +4180,7 @@
       </c>
       <c r="F24" s="238" t="inlineStr">
         <is>
-          <t>Check tap vào card trạng thái "Đang giao" mở đúng màn Chi tiết tin</t>
+          <t>Check bấm vào card trạng thái "Đang giao" mở đúng màn Chi tiết tin</t>
         </is>
       </c>
       <c r="G24" s="238" t="inlineStr">
@@ -4279,7 +4285,7 @@
       </c>
       <c r="F25" s="237" t="inlineStr">
         <is>
-          <t>Check tap vào card trạng thái "Hoàn thành" mở đúng màn Chi tiết tin</t>
+          <t>Check bấm vào card trạng thái "Hoàn thành" mở đúng màn Chi tiết tin</t>
         </is>
       </c>
       <c r="G25" s="237" t="inlineStr">
@@ -4384,7 +4390,7 @@
       </c>
       <c r="F26" s="238" t="inlineStr">
         <is>
-          <t>Check tap vào card "Hết hạn" không cho thao tác</t>
+          <t>Check bấm vào card "Hết hạn" không cho thao tác</t>
         </is>
       </c>
       <c r="G26" s="238" t="inlineStr">
@@ -4474,7 +4480,7 @@
       </c>
       <c r="C27" s="229" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>QA xác nhận app STG (2026-07-28) · C-ORD-06 Resolved</t>
         </is>
       </c>
       <c r="D27" s="229" t="inlineStr">
@@ -4579,7 +4585,7 @@
       </c>
       <c r="C28" s="229" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>QA xác nhận app STG (2026-07-28) · C-ORD-06 Resolved</t>
         </is>
       </c>
       <c r="D28" s="229" t="inlineStr">
@@ -4684,7 +4690,7 @@
       </c>
       <c r="C29" s="205" t="inlineStr">
         <is>
-          <t>Chờ BA bổ sung</t>
+          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-27)</t>
         </is>
       </c>
       <c r="D29" s="205" t="inlineStr">
@@ -20457,9 +20463,9 @@
           <t>Quan sát thực tế app — filter theo trạng thái đơn</t>
         </is>
       </c>
-      <c r="D5" s="246" t="inlineStr">
-        <is>
-          <t>✅ 2 (EP-matched, EP-in-transit; EP-posted đã có ở SC-ORD-020)</t>
+      <c r="D5" s="247" t="inlineStr">
+        <is>
+          <t>✅ 3 (EP-mixed-aggregate baseline — data tổng hợp tab; EP-matched; EP-in-transit)</t>
         </is>
       </c>
       <c r="E5" s="243" t="inlineStr">
@@ -20498,7 +20504,7 @@
         </is>
       </c>
       <c r="L5" s="244" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M5" s="244" t="inlineStr">
         <is>
@@ -20522,9 +20528,9 @@
           <t>Quan sát thực tế app — filter theo trạng thái đơn</t>
         </is>
       </c>
-      <c r="D6" s="243" t="inlineStr">
-        <is>
-          <t>N/A: partition Hoàn thành/Hết hạn đã có riêng ở SC-ORD-019/SC-ORD-005 — dedupe</t>
+      <c r="D6" s="247" t="inlineStr">
+        <is>
+          <t>✅ 1 (EP-mixed-aggregate — data tab "Đã hoàn thành"; partition theo từng trạng thái dùng chung với SC-ORD-017/019)</t>
         </is>
       </c>
       <c r="E6" s="243" t="inlineStr">
@@ -20563,11 +20569,11 @@
         </is>
       </c>
       <c r="L6" s="205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="205" t="inlineStr">
         <is>
-          <t>100% (0/0 — dedupe, đã cover qua SC khác)</t>
+          <t>100% (1/1)</t>
         </is>
       </c>
     </row>
@@ -20639,7 +20645,7 @@
     <row r="8">
       <c r="A8" s="205" t="inlineStr">
         <is>
-          <t>SC-ORD-004/005</t>
+          <t>SC-ORD-005</t>
         </is>
       </c>
       <c r="B8" s="242" t="inlineStr">
@@ -20657,9 +20663,9 @@
           <t>N/A: không phải enum domain</t>
         </is>
       </c>
-      <c r="E8" s="246" t="inlineStr">
-        <is>
-          <t>✅ 1 (before-expiry; at/after-expiry = baseline)</t>
+      <c r="E8" s="247" t="inlineStr">
+        <is>
+          <t>✅ 2 (BVA-at-expiry; BVA-before-expiry)</t>
         </is>
       </c>
       <c r="F8" s="243" t="inlineStr">
@@ -20693,11 +20699,11 @@
         </is>
       </c>
       <c r="L8" s="205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" s="205" t="inlineStr">
         <is>
-          <t>100% (2/2, 1 tham chiếu cross-scope)</t>
+          <t>100% (1/1) — SC-ORD-004 (Timeline) KHÔNG thuộc module này, cover tại Coverage Matrix - Đăng tin</t>
         </is>
       </c>
     </row>
@@ -20847,9 +20853,9 @@
           <t>Quan sát thực tế app — status ∈ {Chờ ghép, Đã ghép, Đang giao, Hoàn thành}</t>
         </is>
       </c>
-      <c r="D11" s="246" t="inlineStr">
-        <is>
-          <t>✅ 3 (EP-matched, EP-in-transit, EP-completed; EP-posted = baseline)</t>
+      <c r="D11" s="247" t="inlineStr">
+        <is>
+          <t>✅ 4 (EP-posted; EP-matched; EP-in-transit; EP-completed)</t>
         </is>
       </c>
       <c r="E11" s="243" t="inlineStr">
@@ -20888,7 +20894,7 @@
         </is>
       </c>
       <c r="L11" s="244" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="244" t="inlineStr">
         <is>
@@ -20977,9 +20983,9 @@
           <t>Quan sát thực tế app / QA đề xuất — C-ORD-06, tab ∈ {Đang diễn ra, Đã hoàn thành}</t>
         </is>
       </c>
-      <c r="D13" s="246" t="inlineStr">
-        <is>
-          <t>✅ 1 (EP-tab-ongoing-empty; EP-tab-completed-empty = baseline retag, theo Project_rule §10.2 style)</t>
+      <c r="D13" s="247" t="inlineStr">
+        <is>
+          <t>✅ 2 (EP-tab-ongoing-empty; EP-tab-completed-empty — tách theo tab per Project_rule §10.2)</t>
         </is>
       </c>
       <c r="E13" s="243" t="inlineStr">
@@ -21018,7 +21024,7 @@
         </is>
       </c>
       <c r="L13" s="244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="244" t="inlineStr">
         <is>
@@ -21091,6 +21097,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="205" t="inlineStr">
         <is>
@@ -21108,7 +21115,7 @@
     <row r="18">
       <c r="A18" s="205" t="inlineStr">
         <is>
-          <t>Most-applied technique: B1 EP (SC-ORD-017: 2, SC-ORD-021: 3, SC-ORD-023: 1) / B2 BVA (SC-ORD-004/005: 1)</t>
+          <t>Most-applied technique: B1 EP (SC-ORD-017: 3, SC-ORD-021: 4, SC-ORD-023: 2, SC-ORD-026: 1) / B2 BVA (SC-ORD-004/005: 2)</t>
         </is>
       </c>
     </row>

--- a/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hoạt động" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>

--- a/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
+++ b/03_test-cases/v1.0/fragments/TC-HOATDONG-v1.0.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Coverage Matrix" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Test Cases'!$A$6:$U$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoạt động'!$A$6:$U$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Coverage Matrix'!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G12" s="238" t="inlineStr">
         <is>
-          <t>Đã đăng nhập, có đơn ở nhiều trạng thái đang diễn ra (Chờ ghép/Đã ghép/Đang giao) lẫn đơn đã Hoàn thành/Hết hạn</t>
+          <t>Đã đăng nhập, có đơn ở nhiều trạng thái đang diễn ra (Chờ ghép/Đã ghép/Đang giao) lẫn đơn đã Hoàn thành/Hết hạn/Đã huỷ</t>
         </is>
       </c>
       <c r="H12" s="238" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="I12" s="238" t="inlineStr">
         <is>
-          <t>4. Danh sách CHỈ chứa đơn ở trạng thái đang diễn ra (Chờ ghép/Đã ghép/Đang giao); KHÔNG lẫn đơn Hoàn thành/Hết hạn</t>
+          <t>4. Danh sách CHỈ chứa đơn ở trạng thái đang diễn ra (Chờ ghép/Đã ghép/Đang giao/Đã huỷ); KHÔNG lẫn đơn Hoàn thành/Hết hạn</t>
         </is>
       </c>
       <c r="J12" s="229" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="AP12" s="234" t="inlineStr">
         <is>
-          <t>Technique: EP-mixed-aggregate (baseline) | Xem EP-matched/EP-in-transit TC kế tiếp cho từng trạng thái riêng; partition "Chờ ghép" đã có ở SC-ORD-020/021</t>
+          <t>Technique: EP-mixed-aggregate (baseline) | Xem EP-matched/EP-in-transit TC kế tiếp cho từng trạng thái riêng; partition "Chờ ghép" đã có ở SC-ORD-020/021 | Cập nhật 2026-07-30: bổ sung đơn Đã huỷ vào bộ dữ liệu trộn (user xác nhận đơn Đã huỷ CÓ hiển thị ở tab này).</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="B26" s="229" t="inlineStr">
         <is>
-          <t>REQ-ORD-011</t>
+          <t>REQ-ORD-011, REQ-CNL-001</t>
         </is>
       </c>
       <c r="C26" s="229" t="inlineStr">
         <is>
-          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
+          <t>DOC-v1.0-05</t>
         </is>
       </c>
       <c r="D26" s="229" t="inlineStr">
@@ -4390,23 +4390,23 @@
       </c>
       <c r="F26" s="238" t="inlineStr">
         <is>
-          <t>Check bấm vào card "Hết hạn" không cho thao tác</t>
+          <t>Check bấm vào card trạng thái "Đã huỷ" mở đúng màn Chi tiết tin/Theo dõi đơn</t>
         </is>
       </c>
       <c r="G26" s="238" t="inlineStr">
         <is>
-          <t>Có đơn ở trạng thái "Hết hạn" (EXPIRED) tại tab "Đã hoàn thành"</t>
+          <t>Có đơn ở trạng thái "Đã huỷ", đang hiển thị dạng card tại tab "Đang diễn ra"</t>
         </is>
       </c>
       <c r="H26" s="238" t="inlineStr">
         <is>
-          <t>1. Mở app FoxEco → bấm "Hoạt động" → tab "Đã hoàn thành"
-2. Bấm vào card có badge "Hết hạn"</t>
+          <t>1. Mở app FoxEco → bấm "Hoạt động" → tab "Đang diễn ra"
+2. Bấm vào card có badge "Đã huỷ"</t>
         </is>
       </c>
       <c r="I26" s="238" t="inlineStr">
         <is>
-          <t>2. Không có điều hướng/phản hồi nào xảy ra (card non-clickable)</t>
+          <t>2. Điều hướng đúng sang màn "Chi tiết tin"/"Theo dõi đơn" của đơn đó (giống hành vi các trạng thái khác, KHÁC "Hết hạn")</t>
         </is>
       </c>
       <c r="J26" s="229" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="AP26" s="234" t="inlineStr">
         <is>
-          <t>Technique: EP-invalid-expired (baseline) | Đối chứng cho EP-021 set (partition không hợp lệ/không thao tác được)</t>
+          <t>Technique: EP-actor-cancelled-clickable | Bổ sung 2026-07-30 theo yêu cầu user (QA GiangDC2 xác nhận trực tiếp trên app STG: card "Đã huỷ" CÓ bấm được, khác với card "Hết hạn" — non-clickable). Cùng nhóm SC-ORD-021 (4→5 TC).</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="C27" s="229" t="inlineStr">
         <is>
-          <t>QA xác nhận app STG (2026-07-28) · C-ORD-06 Resolved</t>
+          <t>DOC-v1.0-02 §3.7 + ảnh Hoạt động</t>
         </is>
       </c>
       <c r="D27" s="229" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="E27" s="229" t="inlineStr">
@@ -4495,23 +4495,23 @@
       </c>
       <c r="F27" s="238" t="inlineStr">
         <is>
-          <t>Check empty state hiển thị khi tab "Đang diễn ra" rỗng</t>
+          <t>Check bấm vào card "Hết hạn" không cho thao tác</t>
         </is>
       </c>
       <c r="G27" s="238" t="inlineStr">
         <is>
-          <t>Tài khoản chưa có đơn nào ở trạng thái đang diễn ra (Chờ ghép/Đã ghép/Đang giao)</t>
+          <t>Có đơn ở trạng thái "Hết hạn" (EXPIRED) tại tab "Đã hoàn thành"</t>
         </is>
       </c>
       <c r="H27" s="238" t="inlineStr">
         <is>
-          <t>1. Mở app FoxEco → bấm "Hoạt động"
-2. Mở tab "Đang diễn ra" (không có đơn nào)</t>
+          <t>1. Mở app FoxEco → bấm "Hoạt động" → tab "Đã hoàn thành"
+2. Bấm vào card có badge "Hết hạn"</t>
         </is>
       </c>
       <c r="I27" s="238" t="inlineStr">
         <is>
-          <t>2. Hiển thị text "Hiện tại chưa có dữ liệu" (C-ORD-06, Resolved — QA xác nhận đúng UI thật)</t>
+          <t>2. Không có điều hướng/phản hồi nào xảy ra (card non-clickable)</t>
         </is>
       </c>
       <c r="J27" s="229" t="inlineStr">
@@ -4556,20 +4556,20 @@
       <c r="AK27" s="232" t="n"/>
       <c r="AL27" s="232" t="n"/>
       <c r="AM27" s="233">
-        <f>IF($A27="","",IF(OR($N27="Yes",$S27="Yes",$X27="Yes",$AC27="Yes",$AH27="Yes"),"Yes","No"))</f>
+        <f>IF($A26="","",IF(OR($N26="Yes",$S26="Yes",$X26="Yes",$AC26="Yes",$AH26="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN27" s="233">
-        <f>IF($A27="","",IFERROR(IF($AI27&lt;&gt;"",$AI27,IF($AD27&lt;&gt;"",$AD27,IF($Y27&lt;&gt;"",$Y27,IF($T27&lt;&gt;"",$T27,IF($O27&lt;&gt;"",$O27,""))))),""))</f>
+        <f>IF($A26="","",IFERROR(IF($AI26&lt;&gt;"",$AI26,IF($AD26&lt;&gt;"",$AD26,IF($Y26&lt;&gt;"",$Y26,IF($T26&lt;&gt;"",$T26,IF($O26&lt;&gt;"",$O26,""))))),""))</f>
         <v/>
       </c>
       <c r="AO27" s="233">
-        <f>IFERROR(IF($AJ27&lt;&gt;"",$AJ27,IF($AE27&lt;&gt;"",$AE27,IF($Z27&lt;&gt;"",$Z27,IF($U27&lt;&gt;"",$U27,IF($P27&lt;&gt;"",$P27,""))))),"")</f>
+        <f>IFERROR(IF($AJ26&lt;&gt;"",$AJ26,IF($AE26&lt;&gt;"",$AE26,IF($Z26&lt;&gt;"",$Z26,IF($U26&lt;&gt;"",$U26,IF($P26&lt;&gt;"",$P26,""))))),"")</f>
         <v/>
       </c>
       <c r="AP27" s="234" t="inlineStr">
         <is>
-          <t>Technique: EP-tab-ongoing-empty | Text đã QA xác nhận trực tiếp trên UI thật (2026-07-28) — xem C-ORD-06 (Resolved)</t>
+          <t>Technique: EP-invalid-expired (baseline) | Đối chứng cho EP-021 set (partition không hợp lệ/không thao tác được)</t>
         </is>
       </c>
     </row>
@@ -4600,18 +4600,18 @@
       </c>
       <c r="F28" s="238" t="inlineStr">
         <is>
-          <t>Check empty state hiển thị khi tab "Đã hoàn thành" rỗng</t>
+          <t>Check empty state hiển thị khi tab "Đang diễn ra" rỗng</t>
         </is>
       </c>
       <c r="G28" s="238" t="inlineStr">
         <is>
-          <t>Tài khoản chưa có đơn nào ở trạng thái Hoàn thành/Hết hạn</t>
+          <t>Tài khoản chưa có đơn nào ở trạng thái đang diễn ra (Chờ ghép/Đã ghép/Đang giao)</t>
         </is>
       </c>
       <c r="H28" s="238" t="inlineStr">
         <is>
           <t>1. Mở app FoxEco → bấm "Hoạt động"
-2. Mở tab "Đã hoàn thành" (không có đơn nào)</t>
+2. Mở tab "Đang diễn ra" (không có đơn nào)</t>
         </is>
       </c>
       <c r="I28" s="238" t="inlineStr">
@@ -4661,68 +4661,67 @@
       <c r="AK28" s="232" t="n"/>
       <c r="AL28" s="232" t="n"/>
       <c r="AM28" s="233">
-        <f>IF($A28="","",IF(OR($N28="Yes",$S28="Yes",$X28="Yes",$AC28="Yes",$AH28="Yes"),"Yes","No"))</f>
+        <f>IF($A27="","",IF(OR($N27="Yes",$S27="Yes",$X27="Yes",$AC27="Yes",$AH27="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN28" s="233">
-        <f>IF($A28="","",IFERROR(IF($AI28&lt;&gt;"",$AI28,IF($AD28&lt;&gt;"",$AD28,IF($Y28&lt;&gt;"",$Y28,IF($T28&lt;&gt;"",$T28,IF($O28&lt;&gt;"",$O28,""))))),""))</f>
+        <f>IF($A27="","",IFERROR(IF($AI27&lt;&gt;"",$AI27,IF($AD27&lt;&gt;"",$AD27,IF($Y27&lt;&gt;"",$Y27,IF($T27&lt;&gt;"",$T27,IF($O27&lt;&gt;"",$O27,""))))),""))</f>
         <v/>
       </c>
       <c r="AO28" s="233">
-        <f>IFERROR(IF($AJ28&lt;&gt;"",$AJ28,IF($AE28&lt;&gt;"",$AE28,IF($Z28&lt;&gt;"",$Z28,IF($U28&lt;&gt;"",$U28,IF($P28&lt;&gt;"",$P28,""))))),"")</f>
+        <f>IFERROR(IF($AJ27&lt;&gt;"",$AJ27,IF($AE27&lt;&gt;"",$AE27,IF($Z27&lt;&gt;"",$Z27,IF($U27&lt;&gt;"",$U27,IF($P27&lt;&gt;"",$P27,""))))),"")</f>
         <v/>
       </c>
       <c r="AP28" s="234" t="inlineStr">
         <is>
-          <t>Technique: EP-tab-completed-empty | Text đã QA xác nhận trực tiếp trên UI thật (2026-07-28) — xem C-ORD-06 (Resolved)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" s="206">
+          <t>Technique: EP-tab-ongoing-empty | Text đã QA xác nhận trực tiếp trên UI thật (2026-07-28) — xem C-ORD-06 (Resolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1" s="206">
       <c r="A29" s="229">
         <f>IF(C29="","",$C$2&amp;"."&amp;COUNTA($C$8:C29)&amp;"")</f>
         <v/>
       </c>
-      <c r="B29" s="236" t="inlineStr">
-        <is>
-          <t>REQ-ORD-011, REQ-CNL-001</t>
-        </is>
-      </c>
-      <c r="C29" s="205" t="inlineStr">
-        <is>
-          <t>Quan sát thực tế app STG (QA GiangDC2, chat 2026-07-27)</t>
-        </is>
-      </c>
-      <c r="D29" s="205" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="E29" s="205" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="F29" s="237" t="inlineStr">
-        <is>
-          <t>Check đơn trạng thái "Đã huỷ" không hiển thị tại màn Hoạt động</t>
-        </is>
-      </c>
-      <c r="G29" s="237" t="inlineStr">
-        <is>
-          <t>Có 1 đơn vừa được huỷ (qua popup "Huỷ đơn", bất kỳ vai trò nào)</t>
-        </is>
-      </c>
-      <c r="H29" s="237" t="inlineStr">
-        <is>
-          <t>1. Huỷ 1 đơn đang ở POSTED hoặc MATCHED (xem TC huỷ đơn module CNL)
-2. Mở app FoxEco → bấm "Hoạt động"
-3. Kiểm tra lần lượt cả 2 tab "Đang diễn ra" và "Đã hoàn thành"</t>
-        </is>
-      </c>
-      <c r="I29" s="237" t="inlineStr">
-        <is>
-          <t>3. Đơn vừa huỷ KHÔNG xuất hiện ở cả 2 tab</t>
+      <c r="B29" s="229" t="inlineStr">
+        <is>
+          <t>REQ-ORD-011</t>
+        </is>
+      </c>
+      <c r="C29" s="229" t="inlineStr">
+        <is>
+          <t>QA xác nhận app STG (2026-07-28) · C-ORD-06 Resolved</t>
+        </is>
+      </c>
+      <c r="D29" s="229" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="E29" s="229" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F29" s="238" t="inlineStr">
+        <is>
+          <t>Check empty state hiển thị khi tab "Đã hoàn thành" rỗng</t>
+        </is>
+      </c>
+      <c r="G29" s="238" t="inlineStr">
+        <is>
+          <t>Tài khoản chưa có đơn nào ở trạng thái Hoàn thành/Hết hạn</t>
+        </is>
+      </c>
+      <c r="H29" s="238" t="inlineStr">
+        <is>
+          <t>1. Mở app FoxEco → bấm "Hoạt động"
+2. Mở tab "Đã hoàn thành" (không có đơn nào)</t>
+        </is>
+      </c>
+      <c r="I29" s="238" t="inlineStr">
+        <is>
+          <t>2. Hiển thị text "Hiện tại chưa có dữ liệu" (C-ORD-06, Resolved — QA xác nhận đúng UI thật)</t>
         </is>
       </c>
       <c r="J29" s="229" t="inlineStr">
@@ -4767,32 +4766,85 @@
       <c r="AK29" s="232" t="n"/>
       <c r="AL29" s="232" t="n"/>
       <c r="AM29" s="233">
-        <f>IF($A29="","",IF(OR($N29="Yes",$S29="Yes",$X29="Yes",$AC29="Yes",$AH29="Yes"),"Yes","No"))</f>
+        <f>IF($A28="","",IF(OR($N28="Yes",$S28="Yes",$X28="Yes",$AC28="Yes",$AH28="Yes"),"Yes","No"))</f>
         <v/>
       </c>
       <c r="AN29" s="233">
-        <f>IF($A29="","",IFERROR(IF($AI29&lt;&gt;"",$AI29,IF($AD29&lt;&gt;"",$AD29,IF($Y29&lt;&gt;"",$Y29,IF($T29&lt;&gt;"",$T29,IF($O29&lt;&gt;"",$O29,""))))),""))</f>
+        <f>IF($A28="","",IFERROR(IF($AI28&lt;&gt;"",$AI28,IF($AD28&lt;&gt;"",$AD28,IF($Y28&lt;&gt;"",$Y28,IF($T28&lt;&gt;"",$T28,IF($O28&lt;&gt;"",$O28,""))))),""))</f>
         <v/>
       </c>
       <c r="AO29" s="233">
-        <f>IFERROR(IF($AJ29&lt;&gt;"",$AJ29,IF($AE29&lt;&gt;"",$AE29,IF($Z29&lt;&gt;"",$Z29,IF($U29&lt;&gt;"",$U29,IF($P29&lt;&gt;"",$P29,""))))),"")</f>
+        <f>IFERROR(IF($AJ28&lt;&gt;"",$AJ28,IF($AE28&lt;&gt;"",$AE28,IF($Z28&lt;&gt;"",$Z28,IF($U28&lt;&gt;"",$U28,IF($P28&lt;&gt;"",$P28,""))))),"")</f>
         <v/>
       </c>
-      <c r="AP29" s="234" t="n"/>
-    </row>
-    <row r="30" ht="60" customHeight="1" s="206">
-      <c r="A30" s="229" t="n"/>
-      <c r="B30" s="229" t="n"/>
-      <c r="C30" s="229" t="n"/>
-      <c r="D30" s="229" t="n"/>
-      <c r="E30" s="229" t="n"/>
-      <c r="F30" s="238" t="n"/>
-      <c r="G30" s="238" t="n"/>
-      <c r="H30" s="238" t="n"/>
-      <c r="I30" s="238" t="n"/>
-      <c r="J30" s="229" t="n"/>
-      <c r="K30" s="229" t="n"/>
-      <c r="L30" s="229" t="n"/>
+      <c r="AP29" s="234" t="inlineStr">
+        <is>
+          <t>Technique: EP-tab-completed-empty | Text đã QA xác nhận trực tiếp trên UI thật (2026-07-28) — xem C-ORD-06 (Resolved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="206">
+      <c r="A30" s="229">
+        <f>IF(C30="","",$C$2&amp;"."&amp;COUNTA($C$8:C30)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="B30" s="236" t="inlineStr">
+        <is>
+          <t>REQ-ORD-011, REQ-CNL-001</t>
+        </is>
+      </c>
+      <c r="C30" s="205" t="inlineStr">
+        <is>
+          <t>DOC-v1.0-05</t>
+        </is>
+      </c>
+      <c r="D30" s="205" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E30" s="205" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F30" s="237" t="inlineStr">
+        <is>
+          <t>Check đơn trạng thái "Đã huỷ" hiển thị đúng dạng card tại tab "Đang diễn ra"</t>
+        </is>
+      </c>
+      <c r="G30" s="237" t="inlineStr">
+        <is>
+          <t>Có 1 đơn vừa được huỷ (qua popup "Huỷ đơn", bất kỳ vai trò nào huỷ)</t>
+        </is>
+      </c>
+      <c r="H30" s="237" t="inlineStr">
+        <is>
+          <t>1. Huỷ 1 đơn đang ở POSTED hoặc MATCHED (xem TC huỷ đơn module CNL)
+2. Mở app FoxEco → bấm "Hoạt động"
+3. Kiểm tra lần lượt cả 2 tab "Đang diễn ra" và "Đã hoàn thành"</t>
+        </is>
+      </c>
+      <c r="I30" s="237" t="inlineStr">
+        <is>
+          <t>3. Đơn vừa huỷ hiển thị ĐÚNG dạng card (badge "Đã huỷ") tại tab "Đang diễn ra"; KHÔNG xuất hiện ở tab "Đã hoàn thành"</t>
+        </is>
+      </c>
+      <c r="J30" s="229" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="K30" s="229" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="L30" s="229" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="M30" s="229" t="n"/>
       <c r="N30" s="231" t="n"/>
       <c r="O30" s="231" t="n"/>
@@ -4819,10 +4871,23 @@
       <c r="AJ30" s="232" t="n"/>
       <c r="AK30" s="232" t="n"/>
       <c r="AL30" s="232" t="n"/>
-      <c r="AM30" s="233" t="n"/>
-      <c r="AN30" s="233" t="n"/>
-      <c r="AO30" s="233" t="n"/>
-      <c r="AP30" s="234" t="n"/>
+      <c r="AM30" s="233">
+        <f>IF($A29="","",IF(OR($N29="Yes",$S29="Yes",$X29="Yes",$AC29="Yes",$AH29="Yes"),"Yes","No"))</f>
+        <v/>
+      </c>
+      <c r="AN30" s="233">
+        <f>IF($A29="","",IFERROR(IF($AI29&lt;&gt;"",$AI29,IF($AD29&lt;&gt;"",$AD29,IF($Y29&lt;&gt;"",$Y29,IF($T29&lt;&gt;"",$T29,IF($O29&lt;&gt;"",$O29,""))))),""))</f>
+        <v/>
+      </c>
+      <c r="AO30" s="233">
+        <f>IFERROR(IF($AJ29&lt;&gt;"",$AJ29,IF($AE29&lt;&gt;"",$AE29,IF($Z29&lt;&gt;"",$Z29,IF($U29&lt;&gt;"",$U29,IF($P29&lt;&gt;"",$P29,""))))),"")</f>
+        <v/>
+      </c>
+      <c r="AP30" s="234" t="inlineStr">
+        <is>
+          <t>⚠ SỬA LẠI 2026-07-30 (user chỉnh, xem CHANGELOG): bản trước ghi "Đã huỷ KHÔNG hiển thị ở cả 2 tab" — SAI so với app thật. QA GiangDC2 xác nhận trực tiếp: đơn Đã huỷ VẪN hiển thị dạng card tại tab "Đang diễn ra" (không biến mất khỏi Hoạt động), chỉ không xuất hiện ở tab "Đã hoàn thành". Technique: EP-actor-cancelled-shown (baseline, sửa lại từ EP-actor-cancelled-hidden).</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="60" customHeight="1" s="206">
       <c r="A31" s="229" t="n"/>
@@ -20894,7 +20959,7 @@
         </is>
       </c>
       <c r="L11" s="244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" s="244" t="inlineStr">
         <is>
@@ -21040,7 +21105,7 @@
       </c>
       <c r="B14" s="242" t="inlineStr">
         <is>
-          <t>Đơn "Đã huỷ" (CNL) không hiển thị tại Hoạt động</t>
+          <t>Đơn "Đã huỷ" (CNL) hiển thị đúng tại tab "Đang diễn ra" (⚠ CORRECTED 2026-07-30)</t>
         </is>
       </c>
       <c r="C14" s="242" t="inlineStr">
@@ -21097,7 +21162,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="205" t="inlineStr">
         <is>
@@ -21108,7 +21172,7 @@
     <row r="17">
       <c r="A17" s="205" t="inlineStr">
         <is>
-          <t>Total TCs (baseline 13 + derived 7): 20</t>
+          <t>Total TCs (baseline 13 + derived 8): 21</t>
         </is>
       </c>
     </row>
